--- a/config/Global Autofill rule.xlsx
+++ b/config/Global Autofill rule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rafael.escalante/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e19a9565cf49a668/Documents/GSM Localization Workflow/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21CEF7D0-1E50-4675-8E14-9097D2A67320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{21CEF7D0-1E50-4675-8E14-9097D2A67320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4694A56A-1F27-4DA5-A2A8-F79C1A23C2A2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30380" windowHeight="17740" firstSheet="3" activeTab="3" xr2:uid="{941B751C-EE5F-488E-BCC8-38A8A1FF0A9C}"/>
+    <workbookView xWindow="-27240" yWindow="1605" windowWidth="25695" windowHeight="14025" activeTab="1" xr2:uid="{941B751C-EE5F-488E-BCC8-38A8A1FF0A9C}"/>
   </bookViews>
   <sheets>
     <sheet name="ADF" sheetId="1" r:id="rId1"/>
@@ -44,45 +44,6 @@
     <t>Global Autofill Tagging</t>
   </si>
   <si>
-    <t>Azure: Proactive</t>
-  </si>
-  <si>
-    <t>Azure: Customer Stories</t>
-  </si>
-  <si>
-    <t>Azure: Culture</t>
-  </si>
-  <si>
-    <t>Azure: Conversation</t>
-  </si>
-  <si>
-    <t>Azure: Solution Plays</t>
-  </si>
-  <si>
-    <t>Azure: Skilling</t>
-  </si>
-  <si>
-    <t>Dev: Proactive</t>
-  </si>
-  <si>
-    <t>Dev: Solution Plays</t>
-  </si>
-  <si>
-    <t>Dev: Customer Stories</t>
-  </si>
-  <si>
-    <t>Dev: Culture</t>
-  </si>
-  <si>
-    <t>Dev: SDC</t>
-  </si>
-  <si>
-    <t>Fabric: Evergreen</t>
-  </si>
-  <si>
-    <t>Fabric: Solution Plays</t>
-  </si>
-  <si>
     <t>Workflow</t>
   </si>
   <si>
@@ -212,36 +173,6 @@
     <t>Products - Microsoft Fabric</t>
   </si>
   <si>
-    <t>C&amp;I: AI Halo</t>
-  </si>
-  <si>
-    <t>C&amp;I: Sustainability</t>
-  </si>
-  <si>
-    <t>C&amp;I: Healthcare</t>
-  </si>
-  <si>
-    <t>C&amp;I: Financial Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C&amp;I: Retail </t>
-  </si>
-  <si>
-    <t>C&amp;I: Manufacturing</t>
-  </si>
-  <si>
-    <t>C&amp;I: Education</t>
-  </si>
-  <si>
-    <t>C&amp;I: Government</t>
-  </si>
-  <si>
-    <t>Security: Skilling</t>
-  </si>
-  <si>
-    <t>Security: Solution Plays</t>
-  </si>
-  <si>
     <t>Line of business (LOB)</t>
   </si>
   <si>
@@ -308,33 +239,6 @@
     <t>Products - Microsoft Security Suite</t>
   </si>
   <si>
-    <t>M365: Evergreen</t>
-  </si>
-  <si>
-    <t>M365: Copilot</t>
-  </si>
-  <si>
-    <t>Teams: Evergreen</t>
-  </si>
-  <si>
-    <t>Teams: Copilot in Teams</t>
-  </si>
-  <si>
-    <t>Power Platform: Evergreen</t>
-  </si>
-  <si>
-    <t>Power Platform: Solution Plays</t>
-  </si>
-  <si>
-    <t>Power BI: Evergreen</t>
-  </si>
-  <si>
-    <t>D365: Evergreen</t>
-  </si>
-  <si>
-    <t>D365: Solution Plays</t>
-  </si>
-  <si>
     <t>Microsoft 365</t>
   </si>
   <si>
@@ -398,33 +302,6 @@
     <t>Products - Dynamics 366</t>
   </si>
   <si>
-    <t>E&amp;A: Ignite - Demand Gen</t>
-  </si>
-  <si>
-    <t>E&amp;A: Build - Demand Gen</t>
-  </si>
-  <si>
-    <t>E&amp;A: Build - Live</t>
-  </si>
-  <si>
-    <t>E&amp;A: AI Tour</t>
-  </si>
-  <si>
-    <t>E&amp;A: 3P Industry</t>
-  </si>
-  <si>
-    <t>E&amp;A: 3P Security</t>
-  </si>
-  <si>
-    <t>E&amp;A: Scale - Azure</t>
-  </si>
-  <si>
-    <t>E&amp;A: Scale - ABS</t>
-  </si>
-  <si>
-    <t>E&amp;A: Scale - Security</t>
-  </si>
-  <si>
     <t>PO/T1</t>
   </si>
   <si>
@@ -462,13 +339,136 @@
   </si>
   <si>
     <t>BDMs, Information Workers</t>
+  </si>
+  <si>
+    <t>Azure - Culture</t>
+  </si>
+  <si>
+    <t>Azure - Conversation</t>
+  </si>
+  <si>
+    <t>Azure - Solution Plays</t>
+  </si>
+  <si>
+    <t>Azure - Skilling</t>
+  </si>
+  <si>
+    <t>Dev - Proactive</t>
+  </si>
+  <si>
+    <t>Dev - Solution Plays</t>
+  </si>
+  <si>
+    <t>Dev - Customer Stories</t>
+  </si>
+  <si>
+    <t>Dev - Culture</t>
+  </si>
+  <si>
+    <t>Dev - SDC</t>
+  </si>
+  <si>
+    <t>Fabric - Evergreen</t>
+  </si>
+  <si>
+    <t>Fabric - Solution Plays</t>
+  </si>
+  <si>
+    <t>Azure - Proactive</t>
+  </si>
+  <si>
+    <t>Azure - Customer Stories</t>
+  </si>
+  <si>
+    <t>C&amp;I - Sustainability</t>
+  </si>
+  <si>
+    <t>C&amp;I - Healthcare</t>
+  </si>
+  <si>
+    <t>C&amp;I - Financial Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C&amp;I - Retail </t>
+  </si>
+  <si>
+    <t>C&amp;I - Manufacturing</t>
+  </si>
+  <si>
+    <t>C&amp;I - Education</t>
+  </si>
+  <si>
+    <t>C&amp;I - Government</t>
+  </si>
+  <si>
+    <t>Security - Skilling</t>
+  </si>
+  <si>
+    <t>Security - Solution Plays</t>
+  </si>
+  <si>
+    <t>M365 - Evergreen</t>
+  </si>
+  <si>
+    <t>M365 - Copilot</t>
+  </si>
+  <si>
+    <t>Teams - Evergreen</t>
+  </si>
+  <si>
+    <t>Teams - Copilot in Teams</t>
+  </si>
+  <si>
+    <t>Power Platform - Evergreen</t>
+  </si>
+  <si>
+    <t>Power Platform - Solution Plays</t>
+  </si>
+  <si>
+    <t>Power BI - Evergreen</t>
+  </si>
+  <si>
+    <t>D365 - Evergreen</t>
+  </si>
+  <si>
+    <t>D365 - Solution Plays</t>
+  </si>
+  <si>
+    <t>E&amp;A - Build - Demand Gen</t>
+  </si>
+  <si>
+    <t>E&amp;A - Build - Live</t>
+  </si>
+  <si>
+    <t>E&amp;A - AI Tour</t>
+  </si>
+  <si>
+    <t>E&amp;A - 3P Industry</t>
+  </si>
+  <si>
+    <t>E&amp;A - 3P Security</t>
+  </si>
+  <si>
+    <t>E&amp;A - Scale - Azure</t>
+  </si>
+  <si>
+    <t>E&amp;A - Scale - ABS</t>
+  </si>
+  <si>
+    <t>E&amp;A - Scale - Security</t>
+  </si>
+  <si>
+    <t>E&amp;A - Ignite - Demand Gen</t>
+  </si>
+  <si>
+    <t>C&amp;I - AI Halo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -883,6 +883,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1201,7 +1205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD7A071-ED7E-4EA5-B221-4C4C9C41AD6D}">
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="17.25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.140625" style="1" customWidth="1"/>
@@ -1221,48 +1225,48 @@
     <col min="29" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="17.25" customHeight="1">
+    <row r="1" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="O1"/>
       <c r="P1"/>
@@ -1279,48 +1283,48 @@
       <c r="AA1"/>
       <c r="AB1"/>
     </row>
-    <row r="2" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="2" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O2" s="14"/>
       <c r="P2" s="14"/>
@@ -1337,48 +1341,48 @@
       <c r="AA2" s="14"/>
       <c r="AB2" s="14"/>
     </row>
-    <row r="3" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="3" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="O3" s="14"/>
       <c r="P3" s="14"/>
@@ -1395,48 +1399,48 @@
       <c r="AA3" s="14"/>
       <c r="AB3" s="14"/>
     </row>
-    <row r="4" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="4" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
@@ -1453,48 +1457,48 @@
       <c r="AA4" s="14"/>
       <c r="AB4" s="14"/>
     </row>
-    <row r="5" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="5" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>
@@ -1511,48 +1515,48 @@
       <c r="AA5" s="14"/>
       <c r="AB5" s="14"/>
     </row>
-    <row r="6" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="6" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="14"/>
@@ -1569,48 +1573,48 @@
       <c r="AA6" s="14"/>
       <c r="AB6" s="14"/>
     </row>
-    <row r="7" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="7" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="14"/>
@@ -1627,48 +1631,48 @@
       <c r="AA7" s="14"/>
       <c r="AB7" s="14"/>
     </row>
-    <row r="8" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="8" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
@@ -1685,48 +1689,48 @@
       <c r="AA8" s="14"/>
       <c r="AB8" s="14"/>
     </row>
-    <row r="9" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="9" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="M9" s="21" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="N9" s="22" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="14"/>
@@ -1743,48 +1747,48 @@
       <c r="AA9" s="14"/>
       <c r="AB9" s="14"/>
     </row>
-    <row r="10" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="10" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="14"/>
@@ -1801,48 +1805,48 @@
       <c r="AA10" s="14"/>
       <c r="AB10" s="14"/>
     </row>
-    <row r="11" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="11" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="N11" s="22" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="14"/>
@@ -1859,48 +1863,48 @@
       <c r="AA11" s="14"/>
       <c r="AB11" s="14"/>
     </row>
-    <row r="12" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="12" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N12" s="22" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="14"/>
@@ -1917,48 +1921,48 @@
       <c r="AA12" s="14"/>
       <c r="AB12" s="14"/>
     </row>
-    <row r="13" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="13" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="M13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="N13" s="22" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="14"/>
@@ -1975,48 +1979,48 @@
       <c r="AA13" s="14"/>
       <c r="AB13" s="14"/>
     </row>
-    <row r="14" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="14" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="L14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="N14" s="22" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="O14" s="14"/>
       <c r="P14" s="14"/>
@@ -2033,48 +2037,48 @@
       <c r="AA14" s="14"/>
       <c r="AB14" s="14"/>
     </row>
-    <row r="15" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="15" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M15" s="22" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="N15" s="22" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="O15" s="14"/>
       <c r="P15" s="14"/>
@@ -2091,48 +2095,48 @@
       <c r="AA15" s="14"/>
       <c r="AB15" s="14"/>
     </row>
-    <row r="16" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1">
+    <row r="16" spans="1:28" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="O16" s="14"/>
       <c r="P16" s="14"/>
@@ -2158,571 +2162,571 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB64F6E7-195D-4FB6-BA95-D6F172A09B6A}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
     <col min="2" max="9" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="30.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18" customHeight="1">
+    <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G6" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H6" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I6" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="E9" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I9" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K9" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" s="39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="C16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A3" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A5" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" s="33" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A6" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A8" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A10" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A11" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A12" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" s="39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A13" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" s="39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A15" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="K15" s="39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1">
-      <c r="A16" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>88</v>
-      </c>
       <c r="K16" s="9" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2733,533 +2737,533 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6F6203-5E58-45D1-9ECC-D6324E58AE98}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="25.140625" defaultRowHeight="17.25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="25.140625" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" customHeight="1">
+    <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:11" ht="17.25" customHeight="1">
+    <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="9"/>
+    </row>
+    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="33"/>
+    </row>
+    <row r="6" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K3" s="9"/>
-    </row>
-    <row r="4" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A4" s="27" t="s">
+      <c r="B6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A5" s="27" t="s">
+      <c r="B7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="28"/>
+    </row>
+    <row r="8" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="I5" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="K5" s="33"/>
-    </row>
-    <row r="6" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A6" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="G6" s="34" t="s">
+      <c r="B8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="9"/>
+    </row>
+    <row r="10" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A7" s="27" t="s">
+      <c r="D10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="C11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="39"/>
+    </row>
+    <row r="12" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="28"/>
-    </row>
-    <row r="8" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="B12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" s="39"/>
+    </row>
+    <row r="13" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="C13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="39"/>
+    </row>
+    <row r="14" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A9" s="27" t="s">
+      <c r="B14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="J9" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="K9" s="9"/>
-    </row>
-    <row r="10" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A10" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A11" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11" s="39"/>
-    </row>
-    <row r="12" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A12" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" s="39"/>
-    </row>
-    <row r="13" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A13" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" s="39"/>
-    </row>
-    <row r="14" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A14" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>50</v>
-      </c>
       <c r="C14" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" ht="17.25" customHeight="1">
+    <row r="15" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="40" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K15" s="39"/>
     </row>
-    <row r="16" spans="1:11" ht="17.25" customHeight="1">
+    <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="K16" s="9"/>
     </row>
@@ -3271,7 +3275,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2307A15-62A3-4687-904F-8968FB6517BB}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="20.42578125" defaultRowHeight="17.25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="20.42578125" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" style="30" customWidth="1"/>
     <col min="2" max="2" width="23.28515625" style="30" bestFit="1" customWidth="1"/>
@@ -3284,548 +3288,548 @@
     <col min="11" max="16384" width="20.42578125" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" customHeight="1">
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="17.25" customHeight="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2" s="28" t="s">
+      <c r="D8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="E8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="F8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="G8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="H8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="I8" s="28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" s="28" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A4" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="H4" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A5" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A6" s="27" t="s">
+      <c r="J8" s="28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A7" s="27" t="s">
+      <c r="B9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B10" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A8" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A9" s="27" t="s">
+      <c r="B11" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="C13" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A10" s="27" t="s">
+      <c r="B14" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="C15" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A11" s="27" t="s">
+      <c r="B16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="C16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="B17" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="C17" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A12" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A13" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="39" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A14" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A15" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="J15" s="39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A16" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A17" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>52</v>
-      </c>
       <c r="D17" s="9" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3834,6 +3838,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100620F8FDCCA89FD4B82BE381E90185D62" ma:contentTypeVersion="27" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bf6660a059724159449dfaf42240375d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="a49b5906-c951-4bc3-9148-5a8d7e486af5" xmlns:ns3="ebe725d4-5a61-4827-9af4-da8e7f768b99" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d26c28753b13251bdbcc123d9a6d5cb4" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4146,7 +4159,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -4161,25 +4174,45 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB192CCC-D7D9-45EA-96EA-1BC07DF673E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66C9633E-A914-441C-B6BC-5139B3ECA043}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D34040E-C1A8-4509-987A-913928F4FFC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB192CCC-D7D9-45EA-96EA-1BC07DF673E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="a49b5906-c951-4bc3-9148-5a8d7e486af5"/>
+    <ds:schemaRef ds:uri="ebe725d4-5a61-4827-9af4-da8e7f768b99"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66C9633E-A914-441C-B6BC-5139B3ECA043}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D34040E-C1A8-4509-987A-913928F4FFC1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="a49b5906-c951-4bc3-9148-5a8d7e486af5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
